--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEW_YORK_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEW_YORK_2021.xlsx
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C236">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C243">
@@ -5413,7 +5413,7 @@
         <v>31</v>
       </c>
       <c r="D281">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="282">
@@ -5791,7 +5791,7 @@
         <v>304</v>
       </c>
       <c r="D302">
-        <v>0.009071648115544151</v>
+        <v>0.009071648115544152</v>
       </c>
     </row>
     <row r="303">
@@ -6277,7 +6277,7 @@
         <v>31</v>
       </c>
       <c r="D329">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="330">
@@ -7231,7 +7231,7 @@
         <v>31</v>
       </c>
       <c r="D382">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="383">
@@ -7717,7 +7717,7 @@
         <v>31</v>
       </c>
       <c r="D409">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="410">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C707">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C708">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C786">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C796">
@@ -22459,7 +22459,7 @@
         <v>31</v>
       </c>
       <c r="D1228">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="1229">
@@ -25663,7 +25663,7 @@
         <v>31</v>
       </c>
       <c r="D1406">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="1407">
@@ -25933,7 +25933,7 @@
         <v>31</v>
       </c>
       <c r="D1421">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="1422">
